--- a/examples/HFP_helen+ruth.xlsx
+++ b/examples/HFP_helen+ruth.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L41"/>
+  <dimension ref="A1:M41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -477,6 +477,11 @@
       </c>
       <c r="L1" t="inlineStr">
         <is>
+          <t>QCD</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
           <t>big-ticket items</t>
         </is>
       </c>
@@ -518,6 +523,9 @@
       <c r="L2" t="n">
         <v>0</v>
       </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -556,6 +564,9 @@
       <c r="L3" t="n">
         <v>0</v>
       </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -594,6 +605,9 @@
       <c r="L4" t="n">
         <v>0</v>
       </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -632,6 +646,9 @@
       <c r="L5" t="n">
         <v>0</v>
       </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -670,6 +687,9 @@
       <c r="L6" t="n">
         <v>0</v>
       </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -708,6 +728,9 @@
       <c r="L7" t="n">
         <v>0</v>
       </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -746,6 +769,9 @@
       <c r="L8" t="n">
         <v>0</v>
       </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -784,6 +810,9 @@
       <c r="L9" t="n">
         <v>0</v>
       </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -822,6 +851,9 @@
       <c r="L10" t="n">
         <v>0</v>
       </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -860,6 +892,9 @@
       <c r="L11" t="n">
         <v>0</v>
       </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -898,6 +933,9 @@
       <c r="L12" t="n">
         <v>0</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -936,6 +974,9 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -974,6 +1015,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1012,6 +1056,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1050,6 +1097,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1088,6 +1138,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1126,6 +1179,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1164,6 +1220,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1202,6 +1261,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1240,6 +1302,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1278,6 +1343,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1316,6 +1384,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1354,6 +1425,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1392,6 +1466,9 @@
       <c r="L25" t="n">
         <v>0</v>
       </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1430,6 +1507,9 @@
       <c r="L26" t="n">
         <v>0</v>
       </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1468,6 +1548,9 @@
       <c r="L27" t="n">
         <v>0</v>
       </c>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1506,6 +1589,9 @@
       <c r="L28" t="n">
         <v>0</v>
       </c>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1544,6 +1630,9 @@
       <c r="L29" t="n">
         <v>0</v>
       </c>
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1582,6 +1671,9 @@
       <c r="L30" t="n">
         <v>0</v>
       </c>
+      <c r="M30" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1620,6 +1712,9 @@
       <c r="L31" t="n">
         <v>0</v>
       </c>
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -1658,6 +1753,9 @@
       <c r="L32" t="n">
         <v>0</v>
       </c>
+      <c r="M32" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1696,6 +1794,9 @@
       <c r="L33" t="n">
         <v>0</v>
       </c>
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -1734,6 +1835,9 @@
       <c r="L34" t="n">
         <v>0</v>
       </c>
+      <c r="M34" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1772,6 +1876,9 @@
       <c r="L35" t="n">
         <v>0</v>
       </c>
+      <c r="M35" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -1810,6 +1917,9 @@
       <c r="L36" t="n">
         <v>0</v>
       </c>
+      <c r="M36" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -1848,6 +1958,9 @@
       <c r="L37" t="n">
         <v>0</v>
       </c>
+      <c r="M37" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -1886,6 +1999,9 @@
       <c r="L38" t="n">
         <v>0</v>
       </c>
+      <c r="M38" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -1924,6 +2040,9 @@
       <c r="L39" t="n">
         <v>0</v>
       </c>
+      <c r="M39" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -1962,6 +2081,9 @@
       <c r="L40" t="n">
         <v>0</v>
       </c>
+      <c r="M40" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -1998,6 +2120,9 @@
         <v>0</v>
       </c>
       <c r="L41" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2012,7 +2137,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L41"/>
+  <dimension ref="A1:M41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2073,6 +2198,11 @@
       </c>
       <c r="L1" t="inlineStr">
         <is>
+          <t>QCD</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
           <t>big-ticket items</t>
         </is>
       </c>
@@ -2114,6 +2244,9 @@
       <c r="L2" t="n">
         <v>0</v>
       </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -2152,6 +2285,9 @@
       <c r="L3" t="n">
         <v>0</v>
       </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -2190,6 +2326,9 @@
       <c r="L4" t="n">
         <v>0</v>
       </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -2228,6 +2367,9 @@
       <c r="L5" t="n">
         <v>0</v>
       </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -2266,6 +2408,9 @@
       <c r="L6" t="n">
         <v>0</v>
       </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -2304,6 +2449,9 @@
       <c r="L7" t="n">
         <v>0</v>
       </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -2342,6 +2490,9 @@
       <c r="L8" t="n">
         <v>0</v>
       </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -2380,6 +2531,9 @@
       <c r="L9" t="n">
         <v>0</v>
       </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -2418,6 +2572,9 @@
       <c r="L10" t="n">
         <v>0</v>
       </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -2456,6 +2613,9 @@
       <c r="L11" t="n">
         <v>0</v>
       </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2494,6 +2654,9 @@
       <c r="L12" t="n">
         <v>0</v>
       </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2532,6 +2695,9 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2570,6 +2736,9 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2608,6 +2777,9 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2646,6 +2818,9 @@
       <c r="L16" t="n">
         <v>0</v>
       </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2684,6 +2859,9 @@
       <c r="L17" t="n">
         <v>0</v>
       </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2722,6 +2900,9 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2760,6 +2941,9 @@
       <c r="L19" t="n">
         <v>0</v>
       </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2798,6 +2982,9 @@
       <c r="L20" t="n">
         <v>0</v>
       </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2836,6 +3023,9 @@
       <c r="L21" t="n">
         <v>0</v>
       </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2874,6 +3064,9 @@
       <c r="L22" t="n">
         <v>0</v>
       </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2912,6 +3105,9 @@
       <c r="L23" t="n">
         <v>0</v>
       </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2950,6 +3146,9 @@
       <c r="L24" t="n">
         <v>0</v>
       </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -2988,6 +3187,9 @@
       <c r="L25" t="n">
         <v>0</v>
       </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3026,6 +3228,9 @@
       <c r="L26" t="n">
         <v>0</v>
       </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3064,6 +3269,9 @@
       <c r="L27" t="n">
         <v>0</v>
       </c>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3102,6 +3310,9 @@
       <c r="L28" t="n">
         <v>0</v>
       </c>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3140,6 +3351,9 @@
       <c r="L29" t="n">
         <v>0</v>
       </c>
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3178,6 +3392,9 @@
       <c r="L30" t="n">
         <v>0</v>
       </c>
+      <c r="M30" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3216,6 +3433,9 @@
       <c r="L31" t="n">
         <v>0</v>
       </c>
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3254,6 +3474,9 @@
       <c r="L32" t="n">
         <v>0</v>
       </c>
+      <c r="M32" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3292,6 +3515,9 @@
       <c r="L33" t="n">
         <v>0</v>
       </c>
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3330,6 +3556,9 @@
       <c r="L34" t="n">
         <v>0</v>
       </c>
+      <c r="M34" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -3368,6 +3597,9 @@
       <c r="L35" t="n">
         <v>0</v>
       </c>
+      <c r="M35" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -3406,6 +3638,9 @@
       <c r="L36" t="n">
         <v>0</v>
       </c>
+      <c r="M36" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -3444,6 +3679,9 @@
       <c r="L37" t="n">
         <v>0</v>
       </c>
+      <c r="M37" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -3482,6 +3720,9 @@
       <c r="L38" t="n">
         <v>0</v>
       </c>
+      <c r="M38" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -3520,6 +3761,9 @@
       <c r="L39" t="n">
         <v>0</v>
       </c>
+      <c r="M39" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -3558,6 +3802,9 @@
       <c r="L40" t="n">
         <v>0</v>
       </c>
+      <c r="M40" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -3594,6 +3841,9 @@
         <v>0</v>
       </c>
       <c r="L41" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" t="n">
         <v>0</v>
       </c>
     </row>

--- a/examples/HFP_helen+ruth.xlsx
+++ b/examples/HFP_helen+ruth.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M41"/>
+  <dimension ref="A1:N41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -477,10 +477,15 @@
       </c>
       <c r="L1" t="inlineStr">
         <is>
+          <t>Roth conv fixed</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
           <t>QCD</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>big-ticket items</t>
         </is>
@@ -520,10 +525,10 @@
       <c r="K2" t="n">
         <v>0</v>
       </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
       <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -561,10 +566,10 @@
       <c r="K3" t="n">
         <v>0</v>
       </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
       <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -602,10 +607,10 @@
       <c r="K4" t="n">
         <v>0</v>
       </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
       <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -643,10 +648,10 @@
       <c r="K5" t="n">
         <v>0</v>
       </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
       <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -684,10 +689,10 @@
       <c r="K6" t="n">
         <v>0</v>
       </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
       <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -725,10 +730,10 @@
       <c r="K7" t="n">
         <v>0</v>
       </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
       <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -766,10 +771,10 @@
       <c r="K8" t="n">
         <v>0</v>
       </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
       <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -807,10 +812,10 @@
       <c r="K9" t="n">
         <v>0</v>
       </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
       <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -848,10 +853,10 @@
       <c r="K10" t="n">
         <v>0</v>
       </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
       <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -889,10 +894,10 @@
       <c r="K11" t="n">
         <v>0</v>
       </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
       <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -930,10 +935,10 @@
       <c r="K12" t="n">
         <v>0</v>
       </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
       <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -971,10 +976,10 @@
       <c r="K13" t="n">
         <v>0</v>
       </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
       <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1012,10 +1017,10 @@
       <c r="K14" t="n">
         <v>0</v>
       </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
       <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1053,10 +1058,10 @@
       <c r="K15" t="n">
         <v>0</v>
       </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
       <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1094,10 +1099,10 @@
       <c r="K16" t="n">
         <v>0</v>
       </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
       <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1135,10 +1140,10 @@
       <c r="K17" t="n">
         <v>0</v>
       </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
       <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1176,10 +1181,10 @@
       <c r="K18" t="n">
         <v>0</v>
       </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
       <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1217,10 +1222,10 @@
       <c r="K19" t="n">
         <v>0</v>
       </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
       <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1258,10 +1263,10 @@
       <c r="K20" t="n">
         <v>0</v>
       </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
       <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1299,10 +1304,10 @@
       <c r="K21" t="n">
         <v>0</v>
       </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
       <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1340,10 +1345,10 @@
       <c r="K22" t="n">
         <v>0</v>
       </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
       <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1381,10 +1386,10 @@
       <c r="K23" t="n">
         <v>0</v>
       </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
       <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1422,10 +1427,10 @@
       <c r="K24" t="n">
         <v>0</v>
       </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
       <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1463,10 +1468,10 @@
       <c r="K25" t="n">
         <v>0</v>
       </c>
-      <c r="L25" t="n">
-        <v>0</v>
-      </c>
       <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1504,10 +1509,10 @@
       <c r="K26" t="n">
         <v>0</v>
       </c>
-      <c r="L26" t="n">
-        <v>0</v>
-      </c>
       <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1545,10 +1550,10 @@
       <c r="K27" t="n">
         <v>0</v>
       </c>
-      <c r="L27" t="n">
-        <v>0</v>
-      </c>
       <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1586,10 +1591,10 @@
       <c r="K28" t="n">
         <v>0</v>
       </c>
-      <c r="L28" t="n">
-        <v>0</v>
-      </c>
       <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1627,10 +1632,10 @@
       <c r="K29" t="n">
         <v>0</v>
       </c>
-      <c r="L29" t="n">
-        <v>0</v>
-      </c>
       <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1668,10 +1673,10 @@
       <c r="K30" t="n">
         <v>0</v>
       </c>
-      <c r="L30" t="n">
-        <v>0</v>
-      </c>
       <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1709,10 +1714,10 @@
       <c r="K31" t="n">
         <v>0</v>
       </c>
-      <c r="L31" t="n">
-        <v>0</v>
-      </c>
       <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1750,10 +1755,10 @@
       <c r="K32" t="n">
         <v>0</v>
       </c>
-      <c r="L32" t="n">
-        <v>0</v>
-      </c>
       <c r="M32" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1791,10 +1796,10 @@
       <c r="K33" t="n">
         <v>0</v>
       </c>
-      <c r="L33" t="n">
-        <v>0</v>
-      </c>
       <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1832,10 +1837,10 @@
       <c r="K34" t="n">
         <v>0</v>
       </c>
-      <c r="L34" t="n">
-        <v>0</v>
-      </c>
       <c r="M34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1873,10 +1878,10 @@
       <c r="K35" t="n">
         <v>0</v>
       </c>
-      <c r="L35" t="n">
-        <v>0</v>
-      </c>
       <c r="M35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1914,10 +1919,10 @@
       <c r="K36" t="n">
         <v>0</v>
       </c>
-      <c r="L36" t="n">
-        <v>0</v>
-      </c>
       <c r="M36" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1955,10 +1960,10 @@
       <c r="K37" t="n">
         <v>0</v>
       </c>
-      <c r="L37" t="n">
-        <v>0</v>
-      </c>
       <c r="M37" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1996,10 +2001,10 @@
       <c r="K38" t="n">
         <v>0</v>
       </c>
-      <c r="L38" t="n">
-        <v>0</v>
-      </c>
       <c r="M38" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2037,10 +2042,10 @@
       <c r="K39" t="n">
         <v>0</v>
       </c>
-      <c r="L39" t="n">
-        <v>0</v>
-      </c>
       <c r="M39" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2078,10 +2083,10 @@
       <c r="K40" t="n">
         <v>0</v>
       </c>
-      <c r="L40" t="n">
-        <v>0</v>
-      </c>
       <c r="M40" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2119,10 +2124,10 @@
       <c r="K41" t="n">
         <v>0</v>
       </c>
-      <c r="L41" t="n">
-        <v>0</v>
-      </c>
       <c r="M41" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2137,7 +2142,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M41"/>
+  <dimension ref="A1:N41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2198,10 +2203,15 @@
       </c>
       <c r="L1" t="inlineStr">
         <is>
+          <t>Roth conv fixed</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
           <t>QCD</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>big-ticket items</t>
         </is>
@@ -2241,10 +2251,10 @@
       <c r="K2" t="n">
         <v>0</v>
       </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
       <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2282,10 +2292,10 @@
       <c r="K3" t="n">
         <v>0</v>
       </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
       <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2323,10 +2333,10 @@
       <c r="K4" t="n">
         <v>0</v>
       </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
       <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2364,10 +2374,10 @@
       <c r="K5" t="n">
         <v>0</v>
       </c>
-      <c r="L5" t="n">
-        <v>0</v>
-      </c>
       <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2405,10 +2415,10 @@
       <c r="K6" t="n">
         <v>0</v>
       </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
       <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2446,10 +2456,10 @@
       <c r="K7" t="n">
         <v>0</v>
       </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
       <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2487,10 +2497,10 @@
       <c r="K8" t="n">
         <v>0</v>
       </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
       <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2528,10 +2538,10 @@
       <c r="K9" t="n">
         <v>0</v>
       </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
       <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2569,10 +2579,10 @@
       <c r="K10" t="n">
         <v>0</v>
       </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
       <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2610,10 +2620,10 @@
       <c r="K11" t="n">
         <v>0</v>
       </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
       <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2651,10 +2661,10 @@
       <c r="K12" t="n">
         <v>0</v>
       </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
       <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2692,10 +2702,10 @@
       <c r="K13" t="n">
         <v>0</v>
       </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
       <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2733,10 +2743,10 @@
       <c r="K14" t="n">
         <v>0</v>
       </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
       <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2774,10 +2784,10 @@
       <c r="K15" t="n">
         <v>0</v>
       </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
       <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2815,10 +2825,10 @@
       <c r="K16" t="n">
         <v>0</v>
       </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
       <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2856,10 +2866,10 @@
       <c r="K17" t="n">
         <v>0</v>
       </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
       <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2897,10 +2907,10 @@
       <c r="K18" t="n">
         <v>0</v>
       </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
       <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2938,10 +2948,10 @@
       <c r="K19" t="n">
         <v>0</v>
       </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
       <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2979,10 +2989,10 @@
       <c r="K20" t="n">
         <v>0</v>
       </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
       <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3020,10 +3030,10 @@
       <c r="K21" t="n">
         <v>0</v>
       </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
       <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3061,10 +3071,10 @@
       <c r="K22" t="n">
         <v>0</v>
       </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
       <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3102,10 +3112,10 @@
       <c r="K23" t="n">
         <v>0</v>
       </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
       <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3143,10 +3153,10 @@
       <c r="K24" t="n">
         <v>0</v>
       </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
       <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3184,10 +3194,10 @@
       <c r="K25" t="n">
         <v>0</v>
       </c>
-      <c r="L25" t="n">
-        <v>0</v>
-      </c>
       <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3225,10 +3235,10 @@
       <c r="K26" t="n">
         <v>0</v>
       </c>
-      <c r="L26" t="n">
-        <v>0</v>
-      </c>
       <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3266,10 +3276,10 @@
       <c r="K27" t="n">
         <v>0</v>
       </c>
-      <c r="L27" t="n">
-        <v>0</v>
-      </c>
       <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3307,10 +3317,10 @@
       <c r="K28" t="n">
         <v>0</v>
       </c>
-      <c r="L28" t="n">
-        <v>0</v>
-      </c>
       <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3348,10 +3358,10 @@
       <c r="K29" t="n">
         <v>0</v>
       </c>
-      <c r="L29" t="n">
-        <v>0</v>
-      </c>
       <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3389,10 +3399,10 @@
       <c r="K30" t="n">
         <v>0</v>
       </c>
-      <c r="L30" t="n">
-        <v>0</v>
-      </c>
       <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3430,10 +3440,10 @@
       <c r="K31" t="n">
         <v>0</v>
       </c>
-      <c r="L31" t="n">
-        <v>0</v>
-      </c>
       <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3471,10 +3481,10 @@
       <c r="K32" t="n">
         <v>0</v>
       </c>
-      <c r="L32" t="n">
-        <v>0</v>
-      </c>
       <c r="M32" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3512,10 +3522,10 @@
       <c r="K33" t="n">
         <v>0</v>
       </c>
-      <c r="L33" t="n">
-        <v>0</v>
-      </c>
       <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3553,10 +3563,10 @@
       <c r="K34" t="n">
         <v>0</v>
       </c>
-      <c r="L34" t="n">
-        <v>0</v>
-      </c>
       <c r="M34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3594,10 +3604,10 @@
       <c r="K35" t="n">
         <v>0</v>
       </c>
-      <c r="L35" t="n">
-        <v>0</v>
-      </c>
       <c r="M35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3635,10 +3645,10 @@
       <c r="K36" t="n">
         <v>0</v>
       </c>
-      <c r="L36" t="n">
-        <v>0</v>
-      </c>
       <c r="M36" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3676,10 +3686,10 @@
       <c r="K37" t="n">
         <v>0</v>
       </c>
-      <c r="L37" t="n">
-        <v>0</v>
-      </c>
       <c r="M37" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3717,10 +3727,10 @@
       <c r="K38" t="n">
         <v>0</v>
       </c>
-      <c r="L38" t="n">
-        <v>0</v>
-      </c>
       <c r="M38" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3758,10 +3768,10 @@
       <c r="K39" t="n">
         <v>0</v>
       </c>
-      <c r="L39" t="n">
-        <v>0</v>
-      </c>
       <c r="M39" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3799,10 +3809,10 @@
       <c r="K40" t="n">
         <v>0</v>
       </c>
-      <c r="L40" t="n">
-        <v>0</v>
-      </c>
       <c r="M40" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3840,10 +3850,10 @@
       <c r="K41" t="n">
         <v>0</v>
       </c>
-      <c r="L41" t="n">
-        <v>0</v>
-      </c>
       <c r="M41" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" t="n">
         <v>0</v>
       </c>
     </row>
